--- a/hourly datasets/cap_gen_year12final.xlsx
+++ b/hourly datasets/cap_gen_year12final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1065553440491354</v>
+        <v>0.10139007847593</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1073220220072553</v>
+        <v>0.103897696327277</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2138773660563906</v>
+        <v>0.205287774803207</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09745546187922861</v>
+        <v>0.0913744145607827</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.204010805928364</v>
+        <v>0.1927644930367127</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0749393821291105</v>
+        <v>0.06399821546440494</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00436756508448804</v>
+        <v>0.003420527164958205</v>
       </c>
       <c r="D5" t="n">
-        <v>15.44556680224815</v>
+        <v>15.51755280839216</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04111302272874021</v>
+        <v>0.03422477673034727</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06635261590659437</v>
+        <v>0.05726709293027755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08352614835162808</v>
+        <v>0.07072933799853157</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1814947261782459</v>
+        <v>0.165388293940335</v>
       </c>
     </row>
     <row r="6">
@@ -559,15 +559,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09806475263741116</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+        <v>0.08662650156580545</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0103823487948846</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.756727120624561</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.008495561589752889</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.06610441871839774</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1071485844132141</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.2046200966865465</v>
+        <v>0.1880165800417355</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +587,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06849091206033495</v>
+        <v>0.04998014688120729</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002193589579185852</v>
+        <v>0.001276502560396264</v>
       </c>
       <c r="D7" t="n">
-        <v>12.79972308625368</v>
+        <v>9.068727283925577</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0101215292127131</v>
+        <v>0.002126942118913714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06418917671874072</v>
+        <v>0.04747672731746898</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07279264740192995</v>
+        <v>0.05248356644494587</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1750462561094703</v>
+        <v>0.1513702253571373</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +615,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04936317317196443</v>
+        <v>0.003460535190222995</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00179921928313599</v>
+        <v>0.0003626630929476222</v>
       </c>
       <c r="D8" t="n">
-        <v>9.896076031876499</v>
+        <v>0.5861591793493889</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008413415385360275</v>
+        <v>0.002156773380734901</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04583505793116451</v>
+        <v>0.002748954359983217</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05289128841276468</v>
+        <v>0.004172116020462676</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1559185172210998</v>
+        <v>0.104850613666153</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +643,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04906988299974192</v>
+        <v>0.003193476526281433</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002040482625462532</v>
+        <v>0.0004974130356131885</v>
       </c>
       <c r="D9" t="n">
-        <v>8.816382794271099</v>
+        <v>0.4785962982411145</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005404991362256598</v>
+        <v>0.002117296709111202</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04506104525694603</v>
+        <v>0.002210170271950429</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0530787207425381</v>
+        <v>0.004176782780612418</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1556252270488773</v>
+        <v>0.1045835550022115</v>
       </c>
     </row>
     <row r="10">
@@ -661,15 +671,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0499486100949007</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+        <v>0.002147066027096977</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0004835692762306169</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1481965080011273</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.002047128118684515</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001191762602698651</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.00310236945149529</v>
+      </c>
       <c r="H10" t="n">
-        <v>0.1565039541440361</v>
+        <v>0.103537144503027</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +699,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03272506821371153</v>
+        <v>0.0310480966029155</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +707,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1392804122628469</v>
+        <v>0.1324381750788455</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +717,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05117392714232886</v>
+        <v>0.05048316332438025</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +725,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1577292711914642</v>
+        <v>0.1518732418003103</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +735,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06807052312645226</v>
+        <v>0.06496192403782393</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +743,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1746258671755876</v>
+        <v>0.166352002513754</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07726985812573917</v>
+        <v>0.07373324444019448</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +761,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1838252021748745</v>
+        <v>0.1751233229161245</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +771,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08069832767537394</v>
+        <v>0.07756227408126855</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +779,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1872536717245093</v>
+        <v>0.1789523525571986</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +789,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08364221506605111</v>
+        <v>0.08084099096653352</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +797,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1901975591151865</v>
+        <v>0.1822310694424635</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +807,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08505360333591129</v>
+        <v>0.08334786565289472</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +815,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1916089473850466</v>
+        <v>0.1847379441288247</v>
       </c>
     </row>
     <row r="18">
@@ -805,22 +825,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1065553440491354</v>
+        <v>-0.10139007847593</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008791455712720293</v>
+        <v>0.008022904965253432</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.91194238406194</v>
+        <v>-19.6627505974483</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02634267328700736</v>
+        <v>0.0259965635288321</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1238444312855709</v>
+        <v>-0.1171586785878144</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0892662568126998</v>
+        <v>-0.08562147836404592</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -833,7 +853,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08784019235903448</v>
+        <v>0.08626024789048305</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +861,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1943955364081698</v>
+        <v>0.1876503263664131</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +871,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08970924313437535</v>
+        <v>0.08797536024522788</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +879,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1962645871835107</v>
+        <v>0.1893654387211579</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +889,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0922956501447684</v>
+        <v>0.09100583648730544</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +897,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1988509941939038</v>
+        <v>0.1923959149632355</v>
       </c>
     </row>
     <row r="22">
@@ -887,7 +907,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09716712440069303</v>
+        <v>0.0955645935379701</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -895,7 +915,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.2037224684498284</v>
+        <v>0.1969546720139001</v>
       </c>
     </row>
     <row r="23">
@@ -905,7 +925,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1017495658785929</v>
+        <v>0.1001354420631533</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -913,7 +933,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2083049099277283</v>
+        <v>0.2015255205390833</v>
       </c>
     </row>
     <row r="24">
@@ -923,7 +943,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1034528816909316</v>
+        <v>0.101647019189025</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -931,7 +951,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.210008225740067</v>
+        <v>0.203037097664955</v>
       </c>
     </row>
     <row r="25">
@@ -941,25 +961,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.104008506325195</v>
+        <v>0.1018860340608983</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007342672136582881</v>
+        <v>0.007138079445277606</v>
       </c>
       <c r="D25" t="n">
-        <v>-464258035.6935544</v>
+        <v>-462286955.5817847</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04584449633748953</v>
+        <v>0.04532407288983376</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08957773653096798</v>
+        <v>0.08785730262102646</v>
       </c>
       <c r="G25" t="n">
-        <v>0.118439276119421</v>
+        <v>0.1159147655007698</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2105638503743303</v>
+        <v>0.2032761125368283</v>
       </c>
     </row>
     <row r="26">
@@ -969,25 +989,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1085442960416581</v>
+        <v>0.1062981854185887</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00716812687958495</v>
+        <v>0.006935788331388843</v>
       </c>
       <c r="D26" t="n">
-        <v>522695178.3343856</v>
+        <v>519801614.1926078</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04100148843186305</v>
+        <v>0.04028068193909527</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0944616594714633</v>
+        <v>0.09267124969602183</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1226269326118539</v>
+        <v>0.1199251211411557</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2150996400907934</v>
+        <v>0.2076882638945187</v>
       </c>
     </row>
     <row r="27">
@@ -997,25 +1017,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1121338848236663</v>
+        <v>0.1093007846994555</v>
       </c>
       <c r="C27" t="n">
-        <v>0.007141991707207579</v>
+        <v>0.006821509214090141</v>
       </c>
       <c r="D27" t="n">
-        <v>25.0630326955693</v>
+        <v>25.18478136188116</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04587700108548545</v>
+        <v>0.04506706110970091</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09810172851232626</v>
+        <v>0.09589854488294802</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1261660411350068</v>
+        <v>0.1227030245159626</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2186892288728016</v>
+        <v>0.2106908631753855</v>
       </c>
     </row>
     <row r="28">
@@ -1025,25 +1045,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1139243743438063</v>
+        <v>0.1115147044913958</v>
       </c>
       <c r="C28" t="n">
-        <v>0.00743520263279721</v>
+        <v>0.007065676424073862</v>
       </c>
       <c r="D28" t="n">
-        <v>431441629.5995058</v>
+        <v>430804399.9152119</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07278981944472064</v>
+        <v>0.07156006525630347</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09931268336114869</v>
+        <v>0.09763043300849177</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1285360653264641</v>
+        <v>0.1253989759743005</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2204797183929417</v>
+        <v>0.2129047829673258</v>
       </c>
     </row>
     <row r="29">
@@ -1053,25 +1073,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.05238793070310608</v>
+        <v>0.002924326239994468</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001886243714204461</v>
+        <v>0.0004902675829999982</v>
       </c>
       <c r="D29" t="n">
-        <v>10.29448615874023</v>
+        <v>0.3237728292828809</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006560674141669946</v>
+        <v>0.001726714541585724</v>
       </c>
       <c r="F29" t="n">
-        <v>0.04868089229358762</v>
+        <v>0.001957341147435675</v>
       </c>
       <c r="G29" t="n">
-        <v>0.05609496911262121</v>
+        <v>0.003891311332553255</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1589432747522414</v>
+        <v>0.1043144047159245</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year12final.xlsx
+++ b/hourly datasets/cap_gen_year12final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2340874049877894</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.10139007847593</v>
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1028290831563334</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.103897696327277</v>
+        <v>0.3753122253661644</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.205287774803207</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2440539035347084</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0913744145607827</v>
+        <v>0.3867319412211541</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1927644930367127</v>
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.255473619389698</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06399821546440494</v>
+        <v>0.4302687603897251</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003420527164958205</v>
+        <v>0.00518993528926208</v>
       </c>
       <c r="D5" t="n">
-        <v>15.51755280839216</v>
+        <v>46.13978479504873</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03422477673034727</v>
+        <v>0.03667791468714628</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05726709293027755</v>
+        <v>0.1686638719385629</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07072933799853157</v>
+        <v>0.1890669553613121</v>
       </c>
       <c r="H5" t="n">
-        <v>0.165388293940335</v>
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.299010438558269</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +576,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08662650156580545</v>
+        <v>0.369112011082363</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0103823487948846</v>
+        <v>0.01840897501664361</v>
       </c>
       <c r="D6" t="n">
-        <v>9.756727120624561</v>
+        <v>12.47961125488317</v>
       </c>
       <c r="E6" t="n">
-        <v>0.008495561589752889</v>
+        <v>0.008534434798919877</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06610441871839774</v>
+        <v>0.09849154148576002</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1071485844132141</v>
+        <v>0.1713111515660798</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1880165800417355</v>
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2378536892509069</v>
       </c>
     </row>
     <row r="7">
@@ -587,25 +607,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04998014688120729</v>
+        <v>0.4926114423947838</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001276502560396264</v>
+        <v>0.005527551560673253</v>
       </c>
       <c r="D7" t="n">
-        <v>9.068727283925577</v>
+        <v>54.80179202905985</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002126942118913714</v>
+        <v>0.002167249708369801</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04747672731746898</v>
+        <v>0.2842291182831819</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05248356644494587</v>
+        <v>0.3059024255429722</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1513702253571373</v>
+        <v>13</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3613531205633277</v>
       </c>
     </row>
     <row r="8">
@@ -615,25 +638,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003460535190222995</v>
+        <v>0.5301555161222741</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0003626630929476222</v>
+        <v>0.00130731880890327</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5861591793493889</v>
+        <v>-3.681573531178289</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002156773380734901</v>
+        <v>0.003135115918277569</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002748954359983217</v>
+        <v>0.006029701965114086</v>
       </c>
       <c r="G8" t="n">
-        <v>0.004172116020462676</v>
+        <v>0.01115670885530198</v>
       </c>
       <c r="H8" t="n">
-        <v>0.104850613666153</v>
+        <v>181</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.398897194290818</v>
       </c>
     </row>
     <row r="9">
@@ -643,25 +669,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003193476526281433</v>
+        <v>0.5314388848519914</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0004974130356131885</v>
+        <v>0.001567794067050533</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4785962982411145</v>
+        <v>-2.764234803540246</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002117296709111202</v>
+        <v>0.002972065907442385</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002210170271950429</v>
+        <v>0.005278025579596162</v>
       </c>
       <c r="G9" t="n">
-        <v>0.004176782780612418</v>
+        <v>0.01144507123292786</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1045835550022115</v>
+        <v>181</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4001805630205354</v>
       </c>
     </row>
     <row r="10">
@@ -671,25 +700,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002147066027096977</v>
+        <v>0.5113554007102381</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0004835692762306169</v>
+        <v>0.001489700530948339</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1481965080011273</v>
+        <v>-41.29951834634402</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002047128118684515</v>
+        <v>0.002504273182621194</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001191762602698651</v>
+        <v>-0.01994670585440357</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00310236945149529</v>
+        <v>-0.0140879888979269</v>
       </c>
       <c r="H10" t="n">
-        <v>0.103537144503027</v>
+        <v>181</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3800970788787821</v>
       </c>
     </row>
     <row r="11">
@@ -699,7 +731,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0310480966029155</v>
+        <v>0.2761447789744947</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -707,7 +739,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1324381750788455</v>
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1448864571430386</v>
       </c>
     </row>
     <row r="12">
@@ -717,7 +752,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05048316332438025</v>
+        <v>0.2961360877167518</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -725,7 +760,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1518732418003103</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1648777658852958</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +773,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06496192403782393</v>
+        <v>0.3120262992411109</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -743,7 +781,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.166352002513754</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1807679774096548</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +794,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07373324444019448</v>
+        <v>0.3236062240659343</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -761,7 +802,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1751233229161245</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1923479022344782</v>
       </c>
     </row>
     <row r="15">
@@ -771,7 +815,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07756227408126855</v>
+        <v>0.3290506924725773</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -779,7 +823,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1789523525571986</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1977923706411212</v>
       </c>
     </row>
     <row r="16">
@@ -789,7 +836,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08084099096653352</v>
+        <v>0.3352463118719688</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -797,7 +844,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1822310694424635</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2039879900405128</v>
       </c>
     </row>
     <row r="17">
@@ -807,7 +857,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08334786565289472</v>
+        <v>0.3383104886570204</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -815,7 +865,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1847379441288247</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2070521668255643</v>
       </c>
     </row>
     <row r="18">
@@ -825,24 +878,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.10139007847593</v>
+        <v>0.1312583218314561</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008022904965253432</v>
+        <v>0.008375302642287292</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.6627505974483</v>
+        <v>-19.99027420429717</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0259965635288321</v>
+        <v>0.02614117794890092</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1171586785878144</v>
+        <v>-0.1204170230575113</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08562147836404592</v>
+        <v>-0.08748677166706804</v>
       </c>
       <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -853,7 +909,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08626024789048305</v>
+        <v>0.3415280462597606</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -861,7 +917,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1876503263664131</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2102697244283046</v>
       </c>
     </row>
     <row r="20">
@@ -871,7 +930,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08797536024522788</v>
+        <v>0.343304613987973</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -879,7 +938,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1893654387211579</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.212046292156517</v>
       </c>
     </row>
     <row r="21">
@@ -889,7 +951,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09100583648730544</v>
+        <v>0.3471462661854318</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -897,7 +959,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1923959149632355</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2158879443539757</v>
       </c>
     </row>
     <row r="22">
@@ -907,7 +972,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0955645935379701</v>
+        <v>0.3536574188770327</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -915,7 +980,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1969546720139001</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2223990970455766</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +993,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1001354420631533</v>
+        <v>0.359442399781187</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
@@ -933,7 +1001,10 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>0.2015255205390833</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.228184077949731</v>
       </c>
     </row>
     <row r="24">
@@ -943,7 +1014,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.101647019189025</v>
+        <v>0.3633044159978085</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -951,7 +1022,10 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.203037097664955</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2320460941663525</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +1035,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1018860340608983</v>
+        <v>0.367011271957973</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007138079445277606</v>
+        <v>0.007114569440284033</v>
       </c>
       <c r="D25" t="n">
-        <v>-462286955.5817847</v>
+        <v>-462141570.2553091</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04532407288983376</v>
+        <v>0.04511830483479839</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08785730262102646</v>
+        <v>0.08778913060593305</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1159147655007698</v>
+        <v>0.1157541657845734</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2032761125368283</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.235752950126517</v>
       </c>
     </row>
     <row r="26">
@@ -989,25 +1066,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1062981854185887</v>
+        <v>0.3701901734141367</v>
       </c>
       <c r="C26" t="n">
-        <v>0.006935788331388843</v>
+        <v>0.006900842118802066</v>
       </c>
       <c r="D26" t="n">
-        <v>519801614.1926078</v>
+        <v>519611636.0144277</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04028068193909527</v>
+        <v>0.03972179615742003</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09267124969602183</v>
+        <v>0.09255676403577366</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1199251211411557</v>
+        <v>0.1196732609652574</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2076882638945187</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2389318515826807</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1097,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1093007846994555</v>
+        <v>0.3773895437604858</v>
       </c>
       <c r="C27" t="n">
-        <v>0.006821509214090141</v>
+        <v>0.00687089302342418</v>
       </c>
       <c r="D27" t="n">
-        <v>25.18478136188116</v>
+        <v>25.29329099133009</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04506706110970091</v>
+        <v>0.04618029326009344</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09589854488294802</v>
+        <v>0.09634520298152029</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1227030245159626</v>
+        <v>0.1233442673025969</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2106908631753855</v>
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2461312219290298</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1128,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1115147044913958</v>
+        <v>0.3781725315097246</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007065676424073862</v>
+        <v>0.006958911149916068</v>
       </c>
       <c r="D28" t="n">
-        <v>430804399.9152119</v>
+        <v>430579391.4566783</v>
       </c>
       <c r="E28" t="n">
-        <v>0.07156006525630347</v>
+        <v>0.06773941940272085</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09763043300849177</v>
+        <v>0.0971827322165608</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1253989759743005</v>
+        <v>0.1245310836190524</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2129047829673258</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2469142096782686</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1159,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002924326239994468</v>
+        <v>0.332201081372052</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0004902675829999982</v>
+        <v>0.003285741131887988</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3237728292828809</v>
+        <v>5.629067394299931</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001726714541585724</v>
+        <v>0.001961685413847834</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001957341147435675</v>
+        <v>0.01491390339726263</v>
       </c>
       <c r="G29" t="n">
-        <v>0.003891311332553255</v>
+        <v>0.02781280787438629</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1043144047159245</v>
+        <v>130</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2009427595405959</v>
       </c>
     </row>
   </sheetData>
